--- a/backend/chatrooms.xlsx
+++ b/backend/chatrooms.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -439,29 +439,9 @@
         <v>ACTIVE</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>CR-1002</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Elec Room</v>
-      </c>
-      <c r="C3" t="str">
-        <v>csbhut11</v>
-      </c>
-      <c r="D3" t="str">
-        <v>CHUNILAL BHUT</v>
-      </c>
-      <c r="E3" t="str">
-        <v>2026-05-15</v>
-      </c>
-      <c r="F3" t="str">
-        <v>ACTIVE</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
 </file>